--- a/reviews/a-envoyer/jlawsongolf-2026-08-31.xlsx
+++ b/reviews/a-envoyer/jlawsongolf-2026-08-31.xlsx
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28T06:09:03</t>
+          <t>2026-08-28T17:14:08</t>
         </is>
       </c>
     </row>
